--- a/output/pdf_financials_xlsx/KCC.xlsx
+++ b/output/pdf_financials_xlsx/KCC.xlsx
@@ -1312,13 +1312,13 @@
         <v>-15.738</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0</v>
+        <v>-2.996</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.76</v>
+        <v>-1.76</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.878</v>
+        <v>-1.878</v>
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
@@ -1326,19 +1326,19 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>9.157</v>
+        <v>-9.157</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.981</v>
+        <v>-1.981</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.07</v>
+        <v>-1.07</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.644</v>
+        <v>-1.644</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>3.856</v>
+        <v>-3.856</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>-2.317</v>
@@ -1620,13 +1620,13 @@
         <v>-7.965</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.498</v>
+        <v>-1.498</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.76</v>
+        <v>-1.76</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.878</v>
+        <v>-1.878</v>
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
@@ -1634,19 +1634,19 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>9.157</v>
+        <v>-9.157</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.981</v>
+        <v>-1.981</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.07</v>
+        <v>-1.07</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.644</v>
+        <v>-1.644</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>3.856</v>
+        <v>-3.856</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-2.317</v>
@@ -1806,13 +1806,13 @@
         <v>-7.965</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.498</v>
+        <v>-1.498</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.76</v>
+        <v>-1.76</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.878</v>
+        <v>-1.878</v>
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
@@ -1820,19 +1820,19 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>9.157</v>
+        <v>-9.157</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1.981</v>
+        <v>-1.981</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1.07</v>
+        <v>-1.07</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.644</v>
+        <v>-1.644</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>3.856</v>
+        <v>-3.856</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>-2.317</v>
@@ -1996,10 +1996,10 @@
         <v>18.964286</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>18.725</v>
+        <v>-18.725</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>19.555556</v>
+        <v>-19.555556</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>228.925</v>
+        <v>-228.925</v>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
@@ -2020,13 +2020,13 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>35.666667</v>
+        <v>-35.666667</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>41.1</v>
+        <v>-41.1</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>55.085714</v>
+        <v>-55.085714</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>77.233333</v>
@@ -2064,13 +2064,13 @@
         <v>-15.738</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0</v>
+        <v>-2.996</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.76</v>
+        <v>-1.76</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.878</v>
+        <v>-1.878</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -2078,19 +2078,19 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>9.157</v>
+        <v>-9.157</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.981</v>
+        <v>-1.981</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1.07</v>
+        <v>-1.07</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.644</v>
+        <v>-1.644</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>3.856</v>
+        <v>-3.856</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-2.317</v>
@@ -2188,13 +2188,13 @@
         <v>-15.738</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0</v>
+        <v>-2.996</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.76</v>
+        <v>-1.76</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.878</v>
+        <v>-1.878</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -2202,19 +2202,19 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>9.157</v>
+        <v>-9.157</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.981</v>
+        <v>-1.981</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.07</v>
+        <v>-1.07</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.644</v>
+        <v>-1.644</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>3.856</v>
+        <v>-3.856</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-2.317</v>
@@ -2341,16 +2341,14 @@
       <c r="B31" s="3" t="n">
         <v>-49.39001143728555</v>
       </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C31" s="3" t="n">
+        <v>-50</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
@@ -2358,19 +2356,19 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>-0</v>
@@ -6418,13 +6416,13 @@
         </is>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>0.118</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>0.118</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>0.118</v>
       </c>
       <c r="K91" s="3" t="n">
         <v>0</v>
@@ -6441,16 +6439,16 @@
         </is>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0</v>
+        <v>-0.284</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>-0.85</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>-0.732</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>0</v>
+        <v>-0.354</v>
       </c>
     </row>
     <row r="92">
@@ -6482,22 +6480,22 @@
         </is>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>7.034</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>7.726</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>9.891999999999999</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>10.667</v>
       </c>
       <c r="N92" s="1" t="inlineStr">
         <is>
@@ -6505,16 +6503,16 @@
         </is>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>14.164</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>14.45</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>14.866</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>16.279</v>
       </c>
     </row>
     <row r="93">
@@ -6892,7 +6890,7 @@
         <v>-1.76</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>1.878</v>
+        <v>-1.878</v>
       </c>
       <c r="F99" s="1" t="inlineStr">
         <is>
@@ -7131,10 +7129,10 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>0</v>
@@ -7148,25 +7146,25 @@
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>-0.053</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
+        <v>-0.042</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0</v>
+        <v>-0.203</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="M103" s="3" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="N103" s="1" t="inlineStr">
         <is>
@@ -7174,16 +7172,16 @@
         </is>
       </c>
       <c r="O103" s="3" t="n">
-        <v>0</v>
+        <v>0.101</v>
       </c>
       <c r="P103" s="3" t="n">
-        <v>0</v>
+        <v>-0.022</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="R103" s="3" t="n">
-        <v>0</v>
+        <v>-0.013</v>
       </c>
     </row>
     <row r="104">
@@ -7317,10 +7315,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.027</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.052</v>
+        <v>0.01</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>-0.096</v>
@@ -7334,25 +7332,25 @@
         </is>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-0.025</v>
+        <v>0.036</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.02</v>
+        <v>0.065</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.133</v>
+        <v>0.08</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.169</v>
+        <v>0.127</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.277</v>
+        <v>0.074</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.447</v>
+        <v>0.635</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0.314</v>
+        <v>-0.36</v>
       </c>
       <c r="N106" s="1" t="inlineStr">
         <is>
@@ -7360,16 +7358,16 @@
         </is>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0.034</v>
+        <v>0.135</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>-0.237</v>
+        <v>-0.259</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0.32</v>
+        <v>0.327</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>-0.435</v>
+        <v>-0.448</v>
       </c>
     </row>
     <row r="107">
@@ -8078,25 +8076,25 @@
         </is>
       </c>
       <c r="G118" s="3" t="n">
-        <v>6.952</v>
+        <v>5.905</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-2.963</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.156</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.061</v>
+        <v>-0.246</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-1.069</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0.662</v>
+        <v>-0.748</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>2.817</v>
+        <v>0.967</v>
       </c>
       <c r="N118" s="1" t="inlineStr">
         <is>
@@ -8104,16 +8102,16 @@
         </is>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-2.924</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0.215</v>
+        <v>-1.278</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-2.202</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-4.257</v>
       </c>
     </row>
     <row r="119">
@@ -9628,7 +9626,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>-</t>
@@ -10794,7 +10796,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -10984,7 +10990,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -11483,7 +11493,11 @@
           <t>Prepaids and deposits (Note 13)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -12192,7 +12206,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -12390,7 +12408,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -13447,7 +13469,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -13645,7 +13671,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -14346,7 +14376,11 @@
           <t>Receivables, prepaids and deposits (Note 7)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -14637,7 +14671,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -14916,7 +14954,11 @@
           <t>Receivables, prepaids and deposits (Note 9)</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -15613,7 +15655,11 @@
           <t>Receivables, prepaids and deposits</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -20609,7 +20655,11 @@
           <t>Receivables, prepaids and deposits 158 37</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -24099,7 +24149,11 @@
           <t>Accounts receivable, prepaids and deposits (note 13)</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E150" s="5" t="n">
         <v>0.204</v>
       </c>
@@ -26634,7 +26688,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -27582,7 +27640,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -32200,7 +32262,11 @@
           <t>Receivables, prepaids and deposits</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -34293,7 +34359,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -43660,7 +43730,11 @@
           <t>Exploration and evaluation asset expenditures (2,787)</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
@@ -49839,7 +49913,11 @@
           <t>Accounts receivable, prepaids and deposits</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E406" s="5" t="n">
         <v>0.036</v>
       </c>
@@ -56421,13 +56499,13 @@
         </is>
       </c>
       <c r="L473" s="5" t="n">
-        <v>1.07</v>
+        <v>-1.07</v>
       </c>
       <c r="M473" s="5" t="n">
-        <v>1.644</v>
+        <v>-1.644</v>
       </c>
       <c r="N473" s="5" t="n">
-        <v>3.856</v>
+        <v>-3.856</v>
       </c>
       <c r="O473" s="5" t="n">
         <v>-2.317</v>
@@ -58887,10 +58965,10 @@
         </is>
       </c>
       <c r="K498" s="5" t="n">
-        <v>1.981</v>
+        <v>-1.981</v>
       </c>
       <c r="L498" s="5" t="n">
-        <v>1.07</v>
+        <v>-1.07</v>
       </c>
       <c r="M498" t="inlineStr">
         <is>
@@ -59686,10 +59764,10 @@
         </is>
       </c>
       <c r="J506" s="5" t="n">
-        <v>9.157</v>
+        <v>-9.157</v>
       </c>
       <c r="K506" s="5" t="n">
-        <v>1.981</v>
+        <v>-1.981</v>
       </c>
       <c r="L506" t="inlineStr">
         <is>
@@ -63213,7 +63291,7 @@
         </is>
       </c>
       <c r="H541" s="5" t="n">
-        <v>1.878</v>
+        <v>-1.878</v>
       </c>
       <c r="I541" t="inlineStr">
         <is>
@@ -65409,10 +65487,10 @@
         </is>
       </c>
       <c r="F563" s="5" t="n">
-        <v>1.498</v>
+        <v>-1.498</v>
       </c>
       <c r="G563" s="5" t="n">
-        <v>1.76</v>
+        <v>-1.76</v>
       </c>
       <c r="H563" t="inlineStr">
         <is>
@@ -65714,10 +65792,10 @@
         </is>
       </c>
       <c r="F566" s="5" t="n">
-        <v>1.498</v>
+        <v>-1.498</v>
       </c>
       <c r="G566" s="5" t="n">
-        <v>1.76</v>
+        <v>-1.76</v>
       </c>
       <c r="H566" t="inlineStr">
         <is>
@@ -65918,10 +65996,10 @@
         </is>
       </c>
       <c r="F568" s="5" t="n">
-        <v>1.375</v>
+        <v>-1.375</v>
       </c>
       <c r="G568" s="5" t="n">
-        <v>1.76</v>
+        <v>-1.76</v>
       </c>
       <c r="H568" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/KCC.xlsx
+++ b/output/pdf_financials_xlsx/KCC.xlsx
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-15.738</v>
+        <v>-15.733</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-2.996</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-15.738</v>
+        <v>-15.733</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-2.996</v>
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>2.224</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>1.53</v>
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>2.224</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>1.53</v>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="O48" s="3" t="n">
-        <v>2.31</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0.144</v>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -66995,7 +66995,7 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E578" s="5" t="n">

--- a/output/pdf_financials_xlsx/KCC.xlsx
+++ b/output/pdf_financials_xlsx/KCC.xlsx
@@ -7687,16 +7687,16 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.082</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.518</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.043</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.043</v>
       </c>
       <c r="F112" s="1" t="inlineStr">
         <is>
@@ -43837,7 +43837,11 @@
           <t>Proceeds from disposal of property, plant and equipment 69</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E346" t="inlineStr">
         <is>
           <t>-</t>
@@ -48196,7 +48200,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
@@ -50824,7 +50832,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E415" s="5" t="n">
         <v>0.082</v>
       </c>

--- a/output/pdf_financials_xlsx/KCC.xlsx
+++ b/output/pdf_financials_xlsx/KCC.xlsx
@@ -757,7 +757,7 @@
         <v>0.18</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.191</v>
+        <v>0.262</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0.191</v>
@@ -7057,7 +7057,7 @@
         <v>-0.104</v>
       </c>
       <c r="R101" s="3" t="n">
-        <v>-0.111</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="102">
@@ -7367,7 +7367,7 @@
         <v>0.327</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>-0.448</v>
+        <v>-0.303</v>
       </c>
     </row>
     <row r="107">
@@ -7563,10 +7563,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -7580,13 +7580,13 @@
         </is>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.226</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.253</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="J110" s="3" t="n">
         <v>0</v>
@@ -7642,25 +7642,25 @@
         </is>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.029</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.031</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.033</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.027</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.346</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.193</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.172</v>
       </c>
       <c r="N111" s="1" t="inlineStr">
         <is>
@@ -7668,16 +7668,16 @@
         </is>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.067</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="Q111" s="3" t="n">
-        <v>0</v>
+        <v>-0.092</v>
       </c>
       <c r="R111" s="3" t="n">
-        <v>0</v>
+        <v>-0.115</v>
       </c>
     </row>
     <row r="112">
@@ -7879,10 +7879,10 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.179</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.179</v>
       </c>
       <c r="F115" s="1" t="inlineStr">
         <is>
@@ -9100,25 +9100,25 @@
         </is>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.029</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.031</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.033</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.027</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.346</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.193</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.172</v>
       </c>
       <c r="N134" s="1" t="inlineStr">
         <is>
@@ -9126,16 +9126,16 @@
         </is>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.067</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>0</v>
+        <v>-0.092</v>
       </c>
       <c r="R134" s="3" t="n">
-        <v>0</v>
+        <v>-0.115</v>
       </c>
     </row>
     <row r="135">
@@ -9164,25 +9164,25 @@
         </is>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-1.203</v>
+        <v>-1.232</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-0.879</v>
+        <v>-0.91</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-0.713</v>
+        <v>-0.746</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-0.929</v>
+        <v>-0.956</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-1.84</v>
+        <v>-2.186</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-0.746</v>
+        <v>-0.9389999999999999</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-2.093</v>
+        <v>-2.265</v>
       </c>
       <c r="N135" s="1" t="inlineStr">
         <is>
@@ -9190,16 +9190,16 @@
         </is>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-1.119</v>
+        <v>-1.186</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-1.219</v>
+        <v>-1.29</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>-0.882</v>
+        <v>-0.974</v>
       </c>
       <c r="R135" s="3" t="n">
-        <v>-1.628</v>
+        <v>-1.743</v>
       </c>
     </row>
   </sheetData>
@@ -26488,7 +26488,11 @@
           <t>Write-off of GST receivable</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -27353,7 +27357,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -33959,7 +33967,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -34165,7 +34177,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -36056,7 +36072,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -36755,7 +36775,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -39666,7 +39690,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr">
         <is>
           <t>-</t>
@@ -43942,7 +43970,11 @@
           <t>Proceeds on sale of investments -</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E347" t="inlineStr">
         <is>
           <t>-</t>
@@ -47998,7 +48030,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr">
         <is>
           <t>-</t>
@@ -49022,7 +49058,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E397" s="5" t="n">
         <v>0.015</v>
       </c>
@@ -49121,7 +49161,11 @@
           <t>Future income tax expense</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr"/>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E398" s="5" t="n">
         <v>0.192</v>
       </c>
@@ -50525,7 +50569,11 @@
           <t>Issue of shares for private placement</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E412" s="5" t="n">
         <v>2.596</v>
       </c>
@@ -63888,7 +63936,11 @@
           <t>Directors fees</t>
         </is>
       </c>
-      <c r="D547" t="inlineStr"/>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E547" t="inlineStr">
         <is>
           <t>-</t>
